--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>启动包任务：Figma 装好画 1 页框线；建简历骨架（一页纸）</t>
+          <t>俞军第1部分精读 + PE Guide前三章 + 简历量化</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -1598,12 +1598,12 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>启动包任务：Figma 装好画 1 页框线；建简历骨架（一页纸）</t>
+          <t>俞军第2部分 + PE Guide第4-5章 + L1技术选型草稿</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>woshipm 精读 1 篇 + 笔记</t>
+          <t>L1技术选型文档草稿（streamlit/trafilatura/PyMuPDF/中转API）</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>★ 集中推进：Figma 装好画 1 页框线；建简历骨架（一页纸）</t>
+          <t>俞军第3部分交易模型 + L1提示词初稿（JSON Schema/evidence）</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>课程 / 开源项目源码阅读</t>
+          <t>L1提示词初稿：3个模板 + 结构化输出 + 证据约束</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -1692,12 +1692,12 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>—（周日不推进项目）</t>
+          <t>L1 项目骨架 + 首次真实 API 调用（文本→JSON）</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>—（周日留给面试练习）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>周复盘记录</t>
+          <t>周复盘记录 + 踩坑日志</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>启动包任务：Figma 装好画 1 页框线；建简历骨架（一页纸）</t>
+          <t>L1 三种输入（文本/URL/PDF）+ 失败降级</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>启动包任务：Figma 装好画 1 页框线；建简历骨架（一页纸）</t>
+          <t>L1 三模板接线 + 卡片展示 + 一键导出 Markdown</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -7403,6 +7403,7 @@
         </is>
       </c>
     </row>
+    <row r="128"/>
     <row r="129">
       <c r="E129" s="15" t="inlineStr">
         <is>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7403,6 @@
         </is>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="E129" s="15" t="inlineStr">
         <is>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -1806,7 +1806,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -1833,22 +1833,22 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>推进：选定 L1 项目方向</t>
+          <t>（跳）建评测集准备——并入 10-01 执行</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>课程 / 开源项目源码阅读</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>复习上周录音（15 分钟）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>踩坑日志一行</t>
+          <t>并入处理</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>推进：选定 L1 项目方向</t>
+          <t>建 20 条评测集：构成定义 + 来源 + 录入 + gold 标注</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>推进：选定 L1 项目方向</t>
+          <t>S09 英文 schema 修复 + 复跑；评测集 gold 抽查复核</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -7403,6 +7403,7 @@
         </is>
       </c>
     </row>
+    <row r="128"/>
     <row r="129">
       <c r="E129" s="15" t="inlineStr">
         <is>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -1927,12 +1927,12 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>S09 英文 schema 修复 + 复跑；评测集 gold 抽查复核</t>
+          <t>S09 英文 schema + S17 证据跳句修复，复跑对比</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>woshipm 精读 1 篇 + 笔记</t>
+          <t>—（信息摄入可在通勤完成）</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>★ 集中推进：选定 L1 项目方向</t>
+          <t>失败案例分类成文 + 提示词 v0.3（语言策略等）</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -2021,22 +2021,22 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>—（周日不推进项目）</t>
+          <t>全量 20 条重跑 + 前后对比数字</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>—（周日留给面试练习）</t>
+          <t>woshipm 精读 1 篇 + 笔记</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>练 3 道题 + 录音 + 复盘</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>周复盘记录</t>
+          <t>周复盘 + 踩坑日志</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>推进：选定 L1 项目方向</t>
+          <t>写一页项目说明 docs/L1-1项目说明.md</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>—（信息摄入可在通勤完成）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>推进：选定 L1 项目方向</t>
+          <t>L1 收尾：README/评测方法沉淀 + 上线调研（Streamlit Cloud）</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>推进：L1-1 输入层 + JSON Schema 设计</t>
+          <t>L1 复盘 + L2 预研（文档级）：知识库问答需求与方案</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>复习上周录音（15 分钟）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -1994,7 +1994,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -2041,7 +2041,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -2088,7 +2088,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -2135,7 +2135,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -2182,7 +2182,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>推进：L1-1 输入层 + JSON Schema 设计</t>
+          <t>L2 W1：语料整理 + 分块策略 + 索引跑通</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>—（信息摄入可在通勤完成）</t>
+          <t>—（信息摄入可在通勤时完成）</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>推进：L1-1 输入层 + JSON Schema 设计</t>
+          <t>L2 W1：问答链路 + 引用块返回</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>★ 集中推进：L1-1 输入层 + JSON Schema 设计</t>
+          <t>L2 W2：引用定位到段落 + 拒答逻辑</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>课程 / 开源项目源码阅读</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>—（周日不推进项目）</t>
+          <t>L2 W2：MVP 三功能联调 + 自测</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>—（周日留给面试练习）</t>
+          <t>课程 / 开源项目源码阅读</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>练 3 道题 + 录音 + 复盘</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>周复盘记录</t>
+          <t>周复盘 + 踩坑日志</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>推进：L1-1 输入层 + JSON Schema 设计</t>
+          <t>L2 W3：建 30 条评测集（含 10 条无答案）</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>—（信息摄入可在通勤完成）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>推进：L1-1 输入层 + JSON Schema 设计</t>
+          <t>L2 W3：跑 4 个检索指标 + 失败分类</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>推进：L1-1 完成 + 建 20 条评测集 + 出数字</t>
+          <t>L2 W4：针对性优化 + 前后对比</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>课程 / 开源项目源码阅读</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>复习上周录音（15 分钟）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -2538,12 +2538,12 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>推进：L1-1 完成 + 建 20 条评测集 + 出数字</t>
+          <t>L2 W4：案例①项目说明 + 找 3-5 人试用</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>—（信息摄入可在通勤完成）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>推进：L1-1 完成 + 建 20 条评测集 + 出数字</t>
+          <t>（暂定）L1 已提前完成：空档用于部署上线 + gold 复核（待用户）</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>★ 集中推进：L1-1 完成 + 建 20 条评测集 + 出数字</t>
+          <t>（暂定）L1 已提前完成：空档用于部署上线 + gold 复核（待用户）</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>—（周日不推进项目）</t>
+          <t>（暂定）L1 已提前完成：空档用于部署上线 + gold 复核（待用户）</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>练 3 道题 + 录音 + 复盘</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>推进：L1-1 完成 + 建 20 条评测集 + 出数字</t>
+          <t>（暂定）L1 已提前完成：空档用于部署上线 + gold 复核（待用户）</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>推进：L1-1 完成 + 建 20 条评测集 + 出数字</t>
+          <t>（暂定）L1 已提前完成：空档用于部署上线 + gold 复核（待用户）</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7403,6 @@
         </is>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="E129" s="15" t="inlineStr">
         <is>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -2276,7 +2276,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -2323,7 +2323,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -2370,7 +2370,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -2417,7 +2417,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -2464,7 +2464,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -2558,7 +2558,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>

--- a/plans/AI产品经理学习实践计划表.xlsx
+++ b/plans/AI产品经理学习实践计划表.xlsx
@@ -2605,7 +2605,7 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
